--- a/artfynd/A 37398-2022 artfynd.xlsx
+++ b/artfynd/A 37398-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 37398-2022 artfynd.xlsx
+++ b/artfynd/A 37398-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY21"/>
+  <dimension ref="A1:AY25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>345247</v>
+        <v>141999</v>
       </c>
       <c r="B2" t="n">
-        <v>89405</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91859</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1204</v>
+        <v>112</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>435470.8556668124</v>
+        <v>435445</v>
       </c>
       <c r="R2" t="n">
-        <v>6971182.31247449</v>
+        <v>6971087</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -748,19 +743,9 @@
           <t>2008-05-26</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2008-05-26</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -785,12 +770,12 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Olli Manninen</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Olli Manninen, * Naturskyddare</t>
+          <t>Daniel Rutschman, * Naturskyddare</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -801,15 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>345448</v>
+        <v>142000</v>
       </c>
       <c r="B3" t="n">
-        <v>89405</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91859</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -817,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1204</v>
+        <v>112</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -841,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>435506.8075818748</v>
+        <v>435413</v>
       </c>
       <c r="R3" t="n">
-        <v>6971289.81481253</v>
+        <v>6971237</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -874,19 +854,9 @@
           <t>2008-05-26</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2008-05-26</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -911,12 +881,12 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Olli Manninen</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Olli Manninen, * Naturskyddare</t>
+          <t>Daniel Rutschman, * Naturskyddare</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -927,15 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>345449</v>
+        <v>316235</v>
       </c>
       <c r="B4" t="n">
-        <v>89405</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -943,21 +908,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1204</v>
+        <v>1108</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -967,10 +932,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>435515.3140734116</v>
+        <v>435299</v>
       </c>
       <c r="R4" t="n">
-        <v>6971327.086386084</v>
+        <v>6971007</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1000,21 +965,11 @@
           <t>2008-05-26</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2008-05-26</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -1032,6 +987,11 @@
       <c r="AI4" t="inlineStr">
         <is>
           <t>Avverkat</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Granlåga</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1053,19 +1013,14 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>345453</v>
+        <v>345229</v>
       </c>
       <c r="B5" t="n">
-        <v>89405</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -1093,10 +1048,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>435505.0578630574</v>
+        <v>435564</v>
       </c>
       <c r="R5" t="n">
-        <v>6971409.926702205</v>
+        <v>6971275</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1126,19 +1081,9 @@
           <t>2008-05-26</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2008-05-26</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1163,12 +1108,12 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Olli Manninen</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Olli Manninen, * Naturskyddare</t>
+          <t>Daniel Rutschman, * Naturskyddare</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1179,19 +1124,14 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>345248</v>
+        <v>345247</v>
       </c>
       <c r="B6" t="n">
-        <v>89405</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1219,10 +1159,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>435395.7477771884</v>
+        <v>435471</v>
       </c>
       <c r="R6" t="n">
-        <v>6971199.317103502</v>
+        <v>6971182</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1252,19 +1192,9 @@
           <t>2008-05-26</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2008-05-26</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1305,37 +1235,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>316235</v>
+        <v>345248</v>
       </c>
       <c r="B7" t="n">
-        <v>89387</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1108</v>
+        <v>1204</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1345,10 +1270,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>435299.1347245347</v>
+        <v>435396</v>
       </c>
       <c r="R7" t="n">
-        <v>6971007.167572305</v>
+        <v>6971199</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1378,21 +1303,11 @@
           <t>2008-05-26</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2008-05-26</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1410,11 +1325,6 @@
       <c r="AI7" t="inlineStr">
         <is>
           <t>Avverkat</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Granlåga</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1436,19 +1346,14 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>345456</v>
+        <v>345448</v>
       </c>
       <c r="B8" t="n">
-        <v>89405</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -1476,10 +1381,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>435449.6605401548</v>
+        <v>435507</v>
       </c>
       <c r="R8" t="n">
-        <v>6971545.243969677</v>
+        <v>6971290</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1509,19 +1414,9 @@
           <t>2008-05-26</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2008-05-26</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1562,19 +1457,14 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>345467</v>
+        <v>345449</v>
       </c>
       <c r="B9" t="n">
-        <v>89405</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -1602,10 +1492,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>435597.7398512439</v>
+        <v>435515</v>
       </c>
       <c r="R9" t="n">
-        <v>6971263.826941168</v>
+        <v>6971327</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1635,19 +1525,9 @@
           <t>2008-05-26</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2008-05-26</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1672,12 +1552,12 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Olli Manninen</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Daniel Rutschman, * Naturskyddare</t>
+          <t>Olli Manninen, * Naturskyddare</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
@@ -1688,19 +1568,14 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>345466</v>
+        <v>345453</v>
       </c>
       <c r="B10" t="n">
-        <v>89405</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -1728,10 +1603,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>435507.9078298491</v>
+        <v>435505</v>
       </c>
       <c r="R10" t="n">
-        <v>6971252.810241538</v>
+        <v>6971410</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1761,19 +1636,9 @@
           <t>2008-05-26</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2008-05-26</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1798,12 +1663,12 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Olli Manninen</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Daniel Rutschman, * Naturskyddare</t>
+          <t>Olli Manninen, * Naturskyddare</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
@@ -1814,19 +1679,14 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>345464</v>
+        <v>345456</v>
       </c>
       <c r="B11" t="n">
-        <v>89405</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -1854,10 +1714,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>435446.2950697927</v>
+        <v>435450</v>
       </c>
       <c r="R11" t="n">
-        <v>6971235.304061669</v>
+        <v>6971545</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1887,19 +1747,9 @@
           <t>2008-05-26</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2008-05-26</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1924,12 +1774,12 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Olli Manninen</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Daniel Rutschman, * Naturskyddare</t>
+          <t>Olli Manninen, * Naturskyddare</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
@@ -1940,19 +1790,14 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>345468</v>
+        <v>345464</v>
       </c>
       <c r="B12" t="n">
-        <v>89405</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -1980,10 +1825,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>435632.0987975842</v>
+        <v>435446</v>
       </c>
       <c r="R12" t="n">
-        <v>6971267.260748337</v>
+        <v>6971235</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -2013,19 +1858,9 @@
           <t>2008-05-26</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2008-05-26</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2066,19 +1901,14 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>345229</v>
+        <v>345466</v>
       </c>
       <c r="B13" t="n">
-        <v>89405</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
@@ -2106,10 +1936,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>435563.6591679539</v>
+        <v>435508</v>
       </c>
       <c r="R13" t="n">
-        <v>6971274.541970784</v>
+        <v>6971253</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2139,19 +1969,9 @@
           <t>2008-05-26</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2008-05-26</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2192,37 +2012,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>142000</v>
+        <v>345467</v>
       </c>
       <c r="B14" t="n">
-        <v>89337</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>112</v>
+        <v>1204</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2232,10 +2047,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>435413.4056858304</v>
+        <v>435598</v>
       </c>
       <c r="R14" t="n">
-        <v>6971236.865599682</v>
+        <v>6971264</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2265,19 +2080,9 @@
           <t>2008-05-26</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2008-05-26</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2318,50 +2123,45 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>91841159</v>
+        <v>345468</v>
       </c>
       <c r="B15" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>1204</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Jämtlands län, Jmt</t>
+          <t>Prästbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>435601.1850703823</v>
+        <v>435632</v>
       </c>
       <c r="R15" t="n">
-        <v>6971066.967519336</v>
+        <v>6971267</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2388,27 +2188,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2019-06-01</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2008-05-26</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2019-10-31</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>2008-05-26</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2419,52 +2204,57 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>Avverkat</t>
+        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Via Erland Lindblad</t>
+          <t>Daniel Rutschman, * Naturskyddare</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
+          <t>Naturskyddare</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>91841297</v>
+        <v>91841152</v>
       </c>
       <c r="B16" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -2479,10 +2269,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>435165.9665010545</v>
+        <v>435739</v>
       </c>
       <c r="R16" t="n">
-        <v>6971255.90823228</v>
+        <v>6971195</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2512,24 +2302,14 @@
           <t>2019-06-01</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2019-10-31</t>
         </is>
       </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2560,15 +2340,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>91841152</v>
+        <v>91841159</v>
       </c>
       <c r="B17" t="n">
-        <v>56411</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2576,16 +2351,16 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2600,10 +2375,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>435739.0389247189</v>
+        <v>435601</v>
       </c>
       <c r="R17" t="n">
-        <v>6971194.847051037</v>
+        <v>6971067</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2633,24 +2408,14 @@
           <t>2019-06-01</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2019-10-31</t>
         </is>
       </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Födosökshack</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2681,37 +2446,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>91841302</v>
+        <v>91841297</v>
       </c>
       <c r="B18" t="n">
-        <v>96354</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>221952</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2721,10 +2481,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>435430.9732251486</v>
+        <v>435166</v>
       </c>
       <c r="R18" t="n">
-        <v>6971269.849731034</v>
+        <v>6971256</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2754,19 +2514,14 @@
           <t>2019-06-01</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2019-10-31</t>
         </is>
       </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2800,12 +2555,7 @@
         <v>106029917</v>
       </c>
       <c r="B19" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2845,10 +2595,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>435518.6180496986</v>
+        <v>435519</v>
       </c>
       <c r="R19" t="n">
-        <v>6970728.401884655</v>
+        <v>6970728</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2878,19 +2628,9 @@
           <t>2023-01-16</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2023-01-16</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
@@ -2922,15 +2662,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>106029936</v>
+        <v>106029935</v>
       </c>
       <c r="B20" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2955,20 +2690,16 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr"/>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>honfärgad</t>
-        </is>
-      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N20" t="inlineStr"/>
@@ -2978,10 +2709,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>435672.668452872</v>
+        <v>435570</v>
       </c>
       <c r="R20" t="n">
-        <v>6971354.125670544</v>
+        <v>6970719</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3011,19 +2742,9 @@
           <t>2023-01-16</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2023-01-16</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3050,15 +2771,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>106029937</v>
+        <v>106029936</v>
       </c>
       <c r="B21" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3084,11 +2800,19 @@
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>honfärgad</t>
+        </is>
+      </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N21" t="inlineStr"/>
@@ -3098,10 +2822,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>435277.8438721292</v>
+        <v>435673</v>
       </c>
       <c r="R21" t="n">
-        <v>6971109.868824044</v>
+        <v>6971354</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3131,24 +2855,9 @@
           <t>2023-01-16</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2023-01-16</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>ringhack</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3172,6 +2881,419 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>106029937</v>
+      </c>
+      <c r="B22" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Stavbrännhöjden, Jmt</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>435278</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6971110</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Oviken</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2023-01-16</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2023-01-16</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>ringhack</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>91841154</v>
+      </c>
+      <c r="B23" t="n">
+        <v>58057</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>103031</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Lavskrika</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Perisoreus infaustus</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Jämtlands län, Jmt</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>435480</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6971424</v>
+      </c>
+      <c r="S23" t="n">
+        <v>25</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Oviken</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2019-06-01</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2019-10-31</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Via Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr">
+        <is>
+          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>91841302</v>
+      </c>
+      <c r="B24" t="n">
+        <v>99140</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Jämtlands län, Jmt</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>435431</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6971270</v>
+      </c>
+      <c r="S24" t="n">
+        <v>25</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Oviken</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2019-06-01</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2019-10-31</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Via Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr">
+        <is>
+          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>91841306</v>
+      </c>
+      <c r="B25" t="n">
+        <v>99140</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Jämtlands län, Jmt</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>435586</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6971006</v>
+      </c>
+      <c r="S25" t="n">
+        <v>25</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Oviken</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2019-06-01</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2019-10-31</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Via Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr">
+        <is>
+          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 37398-2022 artfynd.xlsx
+++ b/artfynd/A 37398-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY25"/>
+  <dimension ref="A1:AZ25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -783,6 +788,11 @@
           <t>Naturskyddare</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/141999</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -894,6 +904,11 @@
           <t>Naturskyddare</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/142000</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1010,6 +1025,11 @@
           <t>Naturskyddare</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/316235</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1121,6 +1141,11 @@
           <t>Naturskyddare</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/345229</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1232,6 +1257,11 @@
           <t>Naturskyddare</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/345247</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1343,6 +1373,11 @@
           <t>Naturskyddare</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/345248</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1454,6 +1489,11 @@
           <t>Naturskyddare</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/345448</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1565,6 +1605,11 @@
           <t>Naturskyddare</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/345449</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1676,6 +1721,11 @@
           <t>Naturskyddare</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/345453</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1787,6 +1837,11 @@
           <t>Naturskyddare</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/345456</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1898,6 +1953,11 @@
           <t>Naturskyddare</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/345464</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2009,6 +2069,11 @@
           <t>Naturskyddare</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/345466</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2120,6 +2185,11 @@
           <t>Naturskyddare</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/345467</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2231,6 +2301,11 @@
           <t>Naturskyddare</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/345468</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2337,6 +2412,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91841152</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2443,6 +2523,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91841159</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2549,6 +2634,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91841297</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2659,6 +2749,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106029917</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2768,6 +2863,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106029935</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2881,6 +2981,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106029936</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2991,6 +3096,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106029937</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3092,6 +3202,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91841154</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3193,6 +3308,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91841302</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3294,8 +3414,39 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91841306</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>